--- a/data/trans_dic/Predimed_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 19,23</t>
+          <t>13,71; 19,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,14; 19,01</t>
+          <t>13,94; 19,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,58</t>
+          <t>14,42; 18,45</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 16,63</t>
+          <t>9,1; 16,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 21,91</t>
+          <t>13,75; 21,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 18,49</t>
+          <t>12,74; 18,48</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,41; 26,27</t>
+          <t>18,67; 26,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 24,87</t>
+          <t>19,41; 25,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 24,6</t>
+          <t>20,05; 24,49</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 17,93</t>
+          <t>12,59; 17,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 20,97</t>
+          <t>15,09; 21,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,89</t>
+          <t>14,77; 18,93</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61775; 89599</t>
+          <t>63878; 92356</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98930; 132969</t>
+          <t>97545; 133151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167903; 216561</t>
+          <t>168025; 215036</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>211121; 354773</t>
+          <t>194169; 357103</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>289001; 465336</t>
+          <t>292107; 462981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>544740; 787183</t>
+          <t>542510; 786688</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114064; 162703</t>
+          <t>115623; 161523</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122120; 156962</t>
+          <t>122508; 159158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>247445; 307718</t>
+          <t>250699; 306274</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1146509</t>
+          <t>1146510</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>394760; 577128</t>
+          <t>405391; 577854</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>525812; 724648</t>
+          <t>521253; 725786</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>983555; 1260442</t>
+          <t>985721; 1263603</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,82</t>
+          <t>13,5; 19,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 19,03</t>
+          <t>13,94; 18,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,45</t>
+          <t>14,36; 17,98</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 16,74</t>
+          <t>14,5; 18,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 21,79</t>
+          <t>17,26; 20,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,74; 18,48</t>
+          <t>16,34; 18,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 26,08</t>
+          <t>19,17; 26,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,41; 25,21</t>
+          <t>19,71; 25,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 24,49</t>
+          <t>20,36; 25,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 17,95</t>
+          <t>16,27; 19,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 21,01</t>
+          <t>17,78; 20,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 18,93</t>
+          <t>17,4; 19,23</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114400</t>
+          <t>120669</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189628</t>
+          <t>205380</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63878; 92356</t>
+          <t>69757; 102634</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97545; 133151</t>
+          <t>106326; 138027</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168025; 215036</t>
+          <t>183767; 230092</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>301946</t>
+          <t>334435</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>378592</t>
+          <t>384726</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680538</t>
+          <t>719162</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>194169; 357103</t>
+          <t>299888; 374562</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>292107; 462981</t>
+          <t>352146; 416269</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>542510; 786688</t>
+          <t>671088; 773210</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>136905</t>
+          <t>155776</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>139438</t>
+          <t>157666</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276344</t>
+          <t>313442</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>115623; 161523</t>
+          <t>130856; 182598</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122508; 159158</t>
+          <t>138623; 177900</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>250699; 306274</t>
+          <t>282209; 347514</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>514079</t>
+          <t>574923</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>632430</t>
+          <t>663061</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1146510</t>
+          <t>1237984</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>405391; 577854</t>
+          <t>531634; 625101</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>521253; 725786</t>
+          <t>623319; 710245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>985721; 1263603</t>
+          <t>1178868; 1302760</t>
         </is>
       </c>
     </row>
